--- a/etl/working/RR 2026-06-01.xlsx
+++ b/etl/working/RR 2026-06-01.xlsx
@@ -16,20 +16,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,22 +44,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,37 +420,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Outlook</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>BUY TRADE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SELL TRADE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Prev Close</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>RR Date</t>
         </is>
@@ -477,12 +464,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30-YEAR U.S. TREASURY YIELD</t>
+          <t>30-Year U.S. Treasury Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,8 +481,8 @@
       <c r="F2" t="n">
         <v>4.99</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>46171</v>
+      <c r="G2" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="3">
@@ -506,12 +493,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10-YEAR U.S. TREASURY YIELD</t>
+          <t>10-Year U.S. Treasury Yield</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,8 +510,8 @@
       <c r="F3" t="n">
         <v>4.45</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>46171</v>
+      <c r="G3" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="4">
@@ -535,12 +522,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2-YEAR U.S. TREASURY YIELD</t>
+          <t>2-Year U.S. Treasury Yield</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -552,8 +539,8 @@
       <c r="F4" t="n">
         <v>3.98</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>46171</v>
+      <c r="G4" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="5">
@@ -564,12 +551,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HIGH YIELD</t>
+          <t>High Yield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -581,8 +568,8 @@
       <c r="F5" t="n">
         <v>80.31</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>46171</v>
+      <c r="G5" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="6">
@@ -593,12 +580,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INVESTMENT GRADE CORPORATE BOND ETF</t>
+          <t>Investment Grade Corporate Bond ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -610,8 +597,8 @@
       <c r="F6" t="n">
         <v>109.4</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>46171</v>
+      <c r="G6" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="7">
@@ -627,7 +614,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -639,8 +626,8 @@
       <c r="F7" t="n">
         <v>7580</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>46171</v>
+      <c r="G7" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="8">
@@ -651,12 +638,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NASDAQ COMPOSITE</t>
+          <t>NASDAQ Composite</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -668,8 +655,8 @@
       <c r="F8" t="n">
         <v>26973</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>46171</v>
+      <c r="G8" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="9">
@@ -680,12 +667,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RUSSELL 2000</t>
+          <t>Russell 2000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -697,8 +684,8 @@
       <c r="F9" t="n">
         <v>2919</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>46171</v>
+      <c r="G9" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="10">
@@ -709,12 +696,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SELECT SECTOR SPDR FUND</t>
+          <t>Technology Select Sector SPDR Fund</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -726,8 +713,8 @@
       <c r="F10" t="n">
         <v>191</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>46171</v>
+      <c r="G10" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="11">
@@ -738,12 +725,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SPDR S&amp;P OIL &amp; GAS EXPLORE</t>
+          <t>SPDR S&amp;P Oil &amp; Gas Explore</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -755,8 +742,8 @@
       <c r="F11" t="n">
         <v>164</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>46171</v>
+      <c r="G11" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="12">
@@ -767,12 +754,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>STATE STREET SPDR S&amp;P TELECOM ETF</t>
+          <t>State Street SPDR S&amp;P Telecom ETF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -784,8 +771,8 @@
       <c r="F12" t="n">
         <v>239</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>46171</v>
+      <c r="G12" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="13">
@@ -796,12 +783,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UTILITIES SELECT SECTOR SPDR FUND</t>
+          <t>Utilities Select Sector SPDR Fund</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -813,8 +800,8 @@
       <c r="F13" t="n">
         <v>44.42</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>46171</v>
+      <c r="G13" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="14">
@@ -830,7 +817,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -842,8 +829,8 @@
       <c r="F14" t="n">
         <v>4055</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>46171</v>
+      <c r="G14" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="15">
@@ -854,12 +841,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NIKKEI 225 INDEX</t>
+          <t>Nikkei 225 Index</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -871,8 +858,8 @@
       <c r="F15" t="n">
         <v>66934</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>46171</v>
+      <c r="G15" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="16">
@@ -883,12 +870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GERMAN DAX COMPOSITE</t>
+          <t>German DAX Composite</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -900,8 +887,8 @@
       <c r="F16" t="n">
         <v>25084</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>46171</v>
+      <c r="G16" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="17">
@@ -912,12 +899,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VOLATILITY INDEX</t>
+          <t>Volatility Index</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -929,8 +916,8 @@
       <c r="F17" t="n">
         <v>15.32</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>46171</v>
+      <c r="G17" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="18">
@@ -941,12 +928,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. DOLLAR INDEX</t>
+          <t>U.S. Dollar Index</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -958,8 +945,8 @@
       <c r="F18" t="n">
         <v>98.92</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>46171</v>
+      <c r="G18" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="19">
@@ -970,12 +957,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EURO TO U.S. DOLLAR</t>
+          <t>Euro to U.S. Dollar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -987,8 +974,8 @@
       <c r="F19" t="n">
         <v>1.166</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>46171</v>
+      <c r="G19" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="20">
@@ -999,12 +986,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. DOLLAR TO JAPANESE YEN</t>
+          <t>U.S. Dollar to Japanese Yen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1016,8 +1003,8 @@
       <c r="F20" t="n">
         <v>159.46</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>46171</v>
+      <c r="G20" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="21">
@@ -1028,12 +1015,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BRITISH POUND TO U.S. DOLLAR</t>
+          <t>British Pound to U.S. Dollar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1045,8 +1032,8 @@
       <c r="F21" t="n">
         <v>1.347</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>46171</v>
+      <c r="G21" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="22">
@@ -1057,12 +1044,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CANADIAN DOLLAR TO U.S. DOLLAR</t>
+          <t>Canadian Dollar to U.S. Dollar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1074,8 +1061,8 @@
       <c r="F22" t="n">
         <v>0.724</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>46171</v>
+      <c r="G22" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="23">
@@ -1086,12 +1073,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LIGHT CRUDE OIL CONTINUOUS CONTRACT</t>
+          <t>Light Crude Oil Continuous Contract</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1103,8 +1090,8 @@
       <c r="F23" t="n">
         <v>90.27</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>46171</v>
+      <c r="G23" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="24">
@@ -1115,12 +1102,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BRENT CRUDE OIL CONTINUOUS CONTRACT</t>
+          <t>Brent Crude Oil Continuous Contract</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1132,8 +1119,8 @@
       <c r="F24" t="n">
         <v>94</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>46171</v>
+      <c r="G24" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="25">
@@ -1144,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NATURAL GAS CONTINUOUS CONTRACT</t>
+          <t>Natural Gas Continuous Contract</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1161,8 +1148,8 @@
       <c r="F25" t="n">
         <v>3.38</v>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>46171</v>
+      <c r="G25" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="26">
@@ -1173,12 +1160,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GOLD SPOT PRICE</t>
+          <t>Gold Spot Price</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1190,8 +1177,8 @@
       <c r="F26" t="n">
         <v>4534</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>46171</v>
+      <c r="G26" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="27">
@@ -1202,12 +1189,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COPPER SPOT PRICE</t>
+          <t>Copper Spot Price</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1219,8 +1206,8 @@
       <c r="F27" t="n">
         <v>6.44</v>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>46171</v>
+      <c r="G27" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="28">
@@ -1231,12 +1218,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SILVER SPOT PRICE</t>
+          <t>Silver Spot Price</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1248,8 +1235,8 @@
       <c r="F28" t="n">
         <v>76</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>46171</v>
+      <c r="G28" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="29">
@@ -1260,12 +1247,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MICROSOFT CORP.</t>
+          <t>Microsoft Corp.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1277,8 +1264,8 @@
       <c r="F29" t="n">
         <v>450</v>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>46171</v>
+      <c r="G29" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="30">
@@ -1289,12 +1276,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>APPLE INC.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1306,8 +1293,8 @@
       <c r="F30" t="n">
         <v>312</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>46171</v>
+      <c r="G30" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="31">
@@ -1318,12 +1305,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMAZON INC.</t>
+          <t>Amazon Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1335,8 +1322,8 @@
       <c r="F31" t="n">
         <v>271</v>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>46171</v>
+      <c r="G31" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="32">
@@ -1347,12 +1334,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>META PLATFORMS INC.</t>
+          <t>Meta Platforms Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1364,8 +1351,8 @@
       <c r="F32" t="n">
         <v>633</v>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>46171</v>
+      <c r="G32" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="33">
@@ -1376,12 +1363,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ALPHABET INC.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1393,8 +1380,8 @@
       <c r="F33" t="n">
         <v>380</v>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>46171</v>
+      <c r="G33" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="34">
@@ -1405,12 +1392,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NETFLIX INC.</t>
+          <t>Netflix Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1422,8 +1409,8 @@
       <c r="F34" t="n">
         <v>86</v>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>46171</v>
+      <c r="G34" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="35">
@@ -1434,12 +1421,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TESLA INC.</t>
+          <t>Tesla Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1451,8 +1438,8 @@
       <c r="F35" t="n">
         <v>436</v>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>46171</v>
+      <c r="G35" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="36">
@@ -1463,12 +1450,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NVIDIA CORPORATION</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1480,8 +1467,8 @@
       <c r="F36" t="n">
         <v>211</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>46171</v>
+      <c r="G36" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="37">
@@ -1492,12 +1479,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ORACLE CORPORATION</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1509,8 +1496,8 @@
       <c r="F37" t="n">
         <v>226</v>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>46171</v>
+      <c r="G37" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="38">
@@ -1521,12 +1508,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BITCOIN SPOT PRICE</t>
+          <t>Bitcoin Spot Price</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1538,8 +1525,8 @@
       <c r="F38" t="n">
         <v>72993</v>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>46171</v>
+      <c r="G38" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="39">
@@ -1555,7 +1542,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1567,8 +1554,8 @@
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="2" t="n">
-        <v>46171</v>
+      <c r="G39" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="40">
@@ -1584,7 +1571,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1596,8 +1583,8 @@
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>46171</v>
+      <c r="G40" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="41">
@@ -1613,7 +1600,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1625,8 +1612,8 @@
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="2" t="n">
-        <v>46171</v>
+      <c r="G41" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="42">
@@ -1642,7 +1629,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1654,8 +1641,8 @@
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>46171</v>
+      <c r="G42" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="43">
@@ -1671,7 +1658,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1683,8 +1670,8 @@
       <c r="F43" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="2" t="n">
-        <v>46171</v>
+      <c r="G43" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="44">
@@ -1700,7 +1687,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1712,8 +1699,8 @@
       <c r="F44" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="2" t="n">
-        <v>46171</v>
+      <c r="G44" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="45">
@@ -1729,7 +1716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1741,8 +1728,8 @@
       <c r="F45" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="2" t="n">
-        <v>46171</v>
+      <c r="G45" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="46">
@@ -1758,7 +1745,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1770,8 +1757,8 @@
       <c r="F46" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="2" t="n">
-        <v>46171</v>
+      <c r="G46" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="47">
@@ -1787,7 +1774,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1799,8 +1786,8 @@
       <c r="F47" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="2" t="n">
-        <v>46171</v>
+      <c r="G47" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="48">
@@ -1816,7 +1803,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1828,8 +1815,8 @@
       <c r="F48" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="2" t="n">
-        <v>46171</v>
+      <c r="G48" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="49">
@@ -1845,7 +1832,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1857,8 +1844,8 @@
       <c r="F49" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="2" t="n">
-        <v>46171</v>
+      <c r="G49" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
   </sheetData>
